--- a/rcads/data/xls/21_ItemStems.xlsx
+++ b/rcads/data/xls/21_ItemStems.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_21_ItemStems"/>
   </sheets>
   <definedNames>
-    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3530</definedName>
+    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3710</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3530"/>
+  <dimension ref="A1:E3710"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -378,7 +378,7 @@
         <v>2735</v>
       </c>
       <c r="B2" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -397,7 +397,7 @@
         <v>2736</v>
       </c>
       <c r="B3" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C3" s="0">
         <v>1</v>
@@ -416,7 +416,7 @@
         <v>2737</v>
       </c>
       <c r="B4" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C4" s="0">
         <v>1</v>
@@ -435,7 +435,7 @@
         <v>2738</v>
       </c>
       <c r="B5" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0">
         <v>1</v>
@@ -454,7 +454,7 @@
         <v>2739</v>
       </c>
       <c r="B6" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C6" s="0">
         <v>1</v>
@@ -473,7 +473,7 @@
         <v>2740</v>
       </c>
       <c r="B7" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C7" s="0">
         <v>1</v>
@@ -492,7 +492,7 @@
         <v>2741</v>
       </c>
       <c r="B8" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C8" s="0">
         <v>1</v>
@@ -511,7 +511,7 @@
         <v>2742</v>
       </c>
       <c r="B9" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C9" s="0">
         <v>1</v>
@@ -530,7 +530,7 @@
         <v>2743</v>
       </c>
       <c r="B10" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C10" s="0">
         <v>1</v>
@@ -549,7 +549,7 @@
         <v>2744</v>
       </c>
       <c r="B11" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C11" s="0">
         <v>1</v>
@@ -568,7 +568,7 @@
         <v>2745</v>
       </c>
       <c r="B12" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C12" s="0">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>2746</v>
       </c>
       <c r="B13" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C13" s="0">
         <v>1</v>
@@ -606,7 +606,7 @@
         <v>2747</v>
       </c>
       <c r="B14" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C14" s="0">
         <v>1</v>
@@ -625,7 +625,7 @@
         <v>2748</v>
       </c>
       <c r="B15" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C15" s="0">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>2749</v>
       </c>
       <c r="B16" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C16" s="0">
         <v>1</v>
@@ -663,7 +663,7 @@
         <v>2750</v>
       </c>
       <c r="B17" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C17" s="0">
         <v>1</v>
@@ -682,7 +682,7 @@
         <v>2751</v>
       </c>
       <c r="B18" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C18" s="0">
         <v>1</v>
@@ -701,7 +701,7 @@
         <v>2752</v>
       </c>
       <c r="B19" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C19" s="0">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>2753</v>
       </c>
       <c r="B20" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C20" s="0">
         <v>1</v>
@@ -739,7 +739,7 @@
         <v>2754</v>
       </c>
       <c r="B21" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C21" s="0">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v>2755</v>
       </c>
       <c r="B22" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C22" s="0">
         <v>1</v>
@@ -777,7 +777,7 @@
         <v>2756</v>
       </c>
       <c r="B23" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C23" s="0">
         <v>1</v>
@@ -796,7 +796,7 @@
         <v>2757</v>
       </c>
       <c r="B24" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C24" s="0">
         <v>1</v>
@@ -815,7 +815,7 @@
         <v>2758</v>
       </c>
       <c r="B25" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C25" s="0">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>2759</v>
       </c>
       <c r="B26" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C26" s="0">
         <v>1</v>
@@ -853,7 +853,7 @@
         <v>2760</v>
       </c>
       <c r="B27" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C27" s="0">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>2761</v>
       </c>
       <c r="B28" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C28" s="0">
         <v>1</v>
@@ -891,7 +891,7 @@
         <v>2762</v>
       </c>
       <c r="B29" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C29" s="0">
         <v>1</v>
@@ -910,7 +910,7 @@
         <v>2763</v>
       </c>
       <c r="B30" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C30" s="0">
         <v>1</v>
@@ -929,7 +929,7 @@
         <v>2764</v>
       </c>
       <c r="B31" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C31" s="0">
         <v>1</v>
@@ -948,7 +948,7 @@
         <v>2765</v>
       </c>
       <c r="B32" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C32" s="0">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>2766</v>
       </c>
       <c r="B33" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C33" s="0">
         <v>1</v>
@@ -986,7 +986,7 @@
         <v>2767</v>
       </c>
       <c r="B34" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C34" s="0">
         <v>1</v>
@@ -1005,7 +1005,7 @@
         <v>2768</v>
       </c>
       <c r="B35" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C35" s="0">
         <v>1</v>
@@ -1024,7 +1024,7 @@
         <v>2769</v>
       </c>
       <c r="B36" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C36" s="0">
         <v>1</v>
@@ -1043,7 +1043,7 @@
         <v>2770</v>
       </c>
       <c r="B37" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C37" s="0">
         <v>1</v>
@@ -1062,7 +1062,7 @@
         <v>2771</v>
       </c>
       <c r="B38" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C38" s="0">
         <v>1</v>
@@ -40434,7 +40434,7 @@
       </c>
       <c r="E2102" s="0" t="inlineStr">
         <is>
-          <t>Feeling bad about yourself--or that you are a failure or have let yourself down or your family down</t>
+          <t>Feeling bad about yourself--or that you are a failure or have let yourself or your family down</t>
         </is>
       </c>
     </row>
@@ -40472,7 +40472,7 @@
       </c>
       <c r="E2104" s="0" t="inlineStr">
         <is>
-          <t>Moving or speaking so slowly that other people could hae noticed. Or the opposite--being so fidgety or restless that you have been moving around a lot more than usual</t>
+          <t>Moving or speaking so slowly that other people could have noticed. Or the opposite--being so fidgety or restless that you have been moving around a lot more than usual</t>
         </is>
       </c>
     </row>
@@ -40491,7 +40491,7 @@
       </c>
       <c r="E2105" s="0" t="inlineStr">
         <is>
-          <t>Thoughts that you would be better off dead, or of hurting yourself</t>
+          <t>Thoughts that you would be better off dead or of hurting yourself in some way</t>
         </is>
       </c>
     </row>
@@ -57377,7 +57377,7 @@
       </c>
       <c r="E2988" s="0" t="inlineStr">
         <is>
-          <t>Feeling nervous, anxious, or on edge</t>
+          <t>Feeling nervous, anxious or on edge</t>
         </is>
       </c>
     </row>
@@ -67676,6 +67676,3426 @@
       <c r="E3530" s="0" t="inlineStr">
         <is>
           <t>Em cảm thấy bồn chồn</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3531">
+      <c r="A3531" s="0">
+        <v>3661</v>
+      </c>
+      <c r="B3531" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3531" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3531" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3531" s="0" t="inlineStr">
+        <is>
+          <t>我會擔心事情</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3532">
+      <c r="A3532" s="0">
+        <v>3662</v>
+      </c>
+      <c r="B3532" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3532" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3532" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3532" s="0" t="inlineStr">
+        <is>
+          <t>我感到憂愁或空虛</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3533">
+      <c r="A3533" s="0">
+        <v>3663</v>
+      </c>
+      <c r="B3533" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3533" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3533" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3533" s="0" t="inlineStr">
+        <is>
+          <t>當我遇到問題時, 我的肚子會有古怪的感覺</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3534">
+      <c r="A3534" s="0">
+        <v>3664</v>
+      </c>
+      <c r="B3534" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3534" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3534" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3534" s="0" t="inlineStr">
+        <is>
+          <t>當我覺得自己做某些事做得差時, 我便會擔心</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3535">
+      <c r="A3535" s="0">
+        <v>3665</v>
+      </c>
+      <c r="B3535" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3535" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3535" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3535" s="0" t="inlineStr">
+        <is>
+          <t>我怕一個人單獨在家</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3536">
+      <c r="A3536" s="0">
+        <v>3666</v>
+      </c>
+      <c r="B3536" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3536" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3536" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3536" s="0" t="inlineStr">
+        <is>
+          <t>什麼事都不再好玩的</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3537">
+      <c r="A3537" s="0">
+        <v>3667</v>
+      </c>
+      <c r="B3537" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3537" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3537" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3537" s="0" t="inlineStr">
+        <is>
+          <t>當要測驗時, 我感到害怕</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3538">
+      <c r="A3538" s="0">
+        <v>3668</v>
+      </c>
+      <c r="B3538" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3538" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3538" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3538" s="0" t="inlineStr">
+        <is>
+          <t>當我想某人可能生我的氣時, 我會感到擔憂</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3539">
+      <c r="A3539" s="0">
+        <v>3669</v>
+      </c>
+      <c r="B3539" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3539" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3539" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3539" s="0" t="inlineStr">
+        <is>
+          <t>我擔心我不在父母身邊</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3540">
+      <c r="A3540" s="0">
+        <v>3670</v>
+      </c>
+      <c r="B3540" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3540" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3540" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3540" s="0" t="inlineStr">
+        <is>
+          <t>我會被一些腦海中不好或愚蠢/無聊的意念/形像困擾著</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3541">
+      <c r="A3541" s="0">
+        <v>3671</v>
+      </c>
+      <c r="B3541" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3541" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3541" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3541" s="0" t="inlineStr">
+        <is>
+          <t>我睡得不好</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3542">
+      <c r="A3542" s="0">
+        <v>3672</v>
+      </c>
+      <c r="B3542" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3542" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3542" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3542" s="0" t="inlineStr">
+        <is>
+          <t>我擔心我會在學業方面做得不好</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3543">
+      <c r="A3543" s="0">
+        <v>3673</v>
+      </c>
+      <c r="B3543" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3543" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3543" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3543" s="0" t="inlineStr">
+        <is>
+          <t>我擔心有些可怕的事情會發生在一個家人身上</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3544">
+      <c r="A3544" s="0">
+        <v>3674</v>
+      </c>
+      <c r="B3544" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3544" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3544" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3544" s="0" t="inlineStr">
+        <is>
+          <t>我會突然無緣無故地感到透不到氣</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3545">
+      <c r="A3545" s="0">
+        <v>3675</v>
+      </c>
+      <c r="B3545" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3545" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3545" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3545" s="0" t="inlineStr">
+        <is>
+          <t>我的胃口有問題</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3546">
+      <c r="A3546" s="0">
+        <v>3676</v>
+      </c>
+      <c r="B3546" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3546" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3546" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3546" s="0" t="inlineStr">
+        <is>
+          <t>我必需重複去檢查我會否將事情做得對 (例如: 重複檢查電掣 或門是否鎖了)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3547">
+      <c r="A3547" s="0">
+        <v>3677</v>
+      </c>
+      <c r="B3547" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3547" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3547" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3547" s="0" t="inlineStr">
+        <is>
+          <t>我害怕一個人單獨睡覺</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3548">
+      <c r="A3548" s="0">
+        <v>3678</v>
+      </c>
+      <c r="B3548" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3548" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3548" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3548" s="0" t="inlineStr">
+        <is>
+          <t>我早上返學有困難, 因為我感到緊張或害怕</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3549">
+      <c r="A3549" s="0">
+        <v>3679</v>
+      </c>
+      <c r="B3549" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3549" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3549" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3549" s="0" t="inlineStr">
+        <is>
+          <t>我沒有力氣做任何事</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3550">
+      <c r="A3550" s="0">
+        <v>3680</v>
+      </c>
+      <c r="B3550" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3550" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3550" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3550" s="0" t="inlineStr">
+        <is>
+          <t>我擔心自己看起來愚蠢</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3551">
+      <c r="A3551" s="0">
+        <v>3681</v>
+      </c>
+      <c r="B3551" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3551" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3551" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3551" s="0" t="inlineStr">
+        <is>
+          <t>我常常感到疲倦</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3552">
+      <c r="A3552" s="0">
+        <v>3682</v>
+      </c>
+      <c r="B3552" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3552" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3552" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3552" s="0" t="inlineStr">
+        <is>
+          <t>我擔心有些不好的事情會發生在我身上</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3553">
+      <c r="A3553" s="0">
+        <v>3683</v>
+      </c>
+      <c r="B3553" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3553" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3553" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3553" s="0" t="inlineStr">
+        <is>
+          <t>我不能擺脫腦海中一些不好或愚蠢的思想</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3554">
+      <c r="A3554" s="0">
+        <v>3684</v>
+      </c>
+      <c r="B3554" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3554" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3554" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3554" s="0" t="inlineStr">
+        <is>
+          <t>當我有問題時, 我的心跳得很快</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3555">
+      <c r="A3555" s="0">
+        <v>3685</v>
+      </c>
+      <c r="B3555" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3555" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3555" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3555" s="0" t="inlineStr">
+        <is>
+          <t>我不能清晰地思考</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3556">
+      <c r="A3556" s="0">
+        <v>3686</v>
+      </c>
+      <c r="B3556" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3556" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3556" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3556" s="0" t="inlineStr">
+        <is>
+          <t>我會突然無緣無故地發抖或顫動</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3557">
+      <c r="A3557" s="0">
+        <v>3687</v>
+      </c>
+      <c r="B3557" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3557" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3557" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3557" s="0" t="inlineStr">
+        <is>
+          <t>我擔心一些不好的事情會發生在我身上</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3558">
+      <c r="A3558" s="0">
+        <v>3688</v>
+      </c>
+      <c r="B3558" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3558" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3558" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3558" s="0" t="inlineStr">
+        <is>
+          <t>當我遇到問題, 我感到自己在顫抖或虛弱</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3559">
+      <c r="A3559" s="0">
+        <v>3689</v>
+      </c>
+      <c r="B3559" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3559" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3559" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3559" s="0" t="inlineStr">
+        <is>
+          <t>我覺得自己沒有價值</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3560">
+      <c r="A3560" s="0">
+        <v>3690</v>
+      </c>
+      <c r="B3560" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3560" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3560" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3560" s="0" t="inlineStr">
+        <is>
+          <t>我擔心會犯錯</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3561">
+      <c r="A3561" s="0">
+        <v>3691</v>
+      </c>
+      <c r="B3561" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3561" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3561" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3561" s="0" t="inlineStr">
+        <is>
+          <t>我必需想著一些特別的事(例如: 數字或詞語)去阻止不好的事 情發生</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3562">
+      <c r="A3562" s="0">
+        <v>3692</v>
+      </c>
+      <c r="B3562" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3562" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3562" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3562" s="0" t="inlineStr">
+        <is>
+          <t>我擔心別人對我的看法</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3563">
+      <c r="A3563" s="0">
+        <v>3693</v>
+      </c>
+      <c r="B3563" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3563" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3563" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3563" s="0" t="inlineStr">
+        <is>
+          <t>我害怕身處在擠逼的地方(例如: 商場, 戲院, 巴士,多人的游 樂場)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3564">
+      <c r="A3564" s="0">
+        <v>3694</v>
+      </c>
+      <c r="B3564" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3564" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3564" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3564" s="0" t="inlineStr">
+        <is>
+          <t>我會突然無緣無故地感到非常害怕</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3565">
+      <c r="A3565" s="0">
+        <v>3695</v>
+      </c>
+      <c r="B3565" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3565" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3565" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3565" s="0" t="inlineStr">
+        <is>
+          <t>我擔心將來發生的事情</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3566">
+      <c r="A3566" s="0">
+        <v>3696</v>
+      </c>
+      <c r="B3566" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3566" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3566" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3566" s="0" t="inlineStr">
+        <is>
+          <t>我會突然無緣無故地感到頭暈或昏倒</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3567">
+      <c r="A3567" s="0">
+        <v>3697</v>
+      </c>
+      <c r="B3567" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3567" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3567" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3567" s="0" t="inlineStr">
+        <is>
+          <t>我想到死亡的事</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3568">
+      <c r="A3568" s="0">
+        <v>3698</v>
+      </c>
+      <c r="B3568" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3568" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3568" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3568" s="0" t="inlineStr">
+        <is>
+          <t>我害怕在全班同學面前說話</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3569">
+      <c r="A3569" s="0">
+        <v>3699</v>
+      </c>
+      <c r="B3569" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3569" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3569" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3569" s="0" t="inlineStr">
+        <is>
+          <t>我的心會無緣無故地急促跳動</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3570">
+      <c r="A3570" s="0">
+        <v>3700</v>
+      </c>
+      <c r="B3570" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3570" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3570" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3570" s="0" t="inlineStr">
+        <is>
+          <t>我感到不想作任何走動</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3571">
+      <c r="A3571" s="0">
+        <v>3701</v>
+      </c>
+      <c r="B3571" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3571" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3571" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3571" s="0" t="inlineStr">
+        <is>
+          <t>我擔心我會突然無緣無故地害怕起來</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3572">
+      <c r="A3572" s="0">
+        <v>3702</v>
+      </c>
+      <c r="B3572" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3572" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3572" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3572" s="0" t="inlineStr">
+        <is>
+          <t>我必需要重複做某些事情(例如: 洗手,清潔或要將東西用某种次序擺放)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3573">
+      <c r="A3573" s="0">
+        <v>3703</v>
+      </c>
+      <c r="B3573" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3573" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3573" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3573" s="0" t="inlineStr">
+        <is>
+          <t>我怕自己會在別人面前出醜</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3574">
+      <c r="A3574" s="0">
+        <v>3704</v>
+      </c>
+      <c r="B3574" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3574" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3574" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3574" s="0" t="inlineStr">
+        <is>
+          <t>我必需要將某些事情做到恰當, 以阻止不好的事情發生</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3575">
+      <c r="A3575" s="0">
+        <v>3705</v>
+      </c>
+      <c r="B3575" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3575" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3575" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3575" s="0" t="inlineStr">
+        <is>
+          <t>晚上上床睡覺時, 我會擔心事情</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3576">
+      <c r="A3576" s="0">
+        <v>3706</v>
+      </c>
+      <c r="B3576" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3576" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3576" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3576" s="0" t="inlineStr">
+        <is>
+          <t>如果我不在家留宿, 我便會感到害怕</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3577">
+      <c r="A3577" s="0">
+        <v>3707</v>
+      </c>
+      <c r="B3577" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3577" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3577" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3577" s="0" t="inlineStr">
+        <is>
+          <t>我感到坐立不安</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3578">
+      <c r="A3578" s="0">
+        <v>3708</v>
+      </c>
+      <c r="B3578" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3578" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3578" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3578" s="0" t="inlineStr">
+        <is>
+          <t>Saya berasa sedih atau kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3579">
+      <c r="A3579" s="0">
+        <v>3709</v>
+      </c>
+      <c r="B3579" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3579" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3579" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3579" s="0" t="inlineStr">
+        <is>
+          <t>Saya risau bila saya memikirkan tentang perkara yang telah saya lakukan dengan tidak sempurna.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3580">
+      <c r="A3580" s="0">
+        <v>3710</v>
+      </c>
+      <c r="B3580" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3580" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3580" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3580" s="0" t="inlineStr">
+        <is>
+          <t>Saya akan berasa takut untuk berseorangan di rumah.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3581">
+      <c r="A3581" s="0">
+        <v>3711</v>
+      </c>
+      <c r="B3581" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3581" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3581" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3581" s="0" t="inlineStr">
+        <is>
+          <t>Tiada apa yang menyeronokkan lagi.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3582">
+      <c r="A3582" s="0">
+        <v>3712</v>
+      </c>
+      <c r="B3582" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3582" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3582" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3582" s="0" t="inlineStr">
+        <is>
+          <t>Saya bimbang sesuatu perkara buruk akan berlaku terhadap salah seorang ahli keluarga saya.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3583">
+      <c r="A3583" s="0">
+        <v>3713</v>
+      </c>
+      <c r="B3583" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3583" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3583" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3583" s="0" t="inlineStr">
+        <is>
+          <t>Saya takut untuk berada di tempat sesak (seperti pasaraya, pawagam, bas, taman permainan yang sesak).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3584">
+      <c r="A3584" s="0">
+        <v>3714</v>
+      </c>
+      <c r="B3584" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3584" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3584" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3584" s="0" t="inlineStr">
+        <is>
+          <t>Saya berasa bimbang tentang apa yang orang lain fikir tentang diri saya.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3585">
+      <c r="A3585" s="0">
+        <v>3715</v>
+      </c>
+      <c r="B3585" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3585" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3585" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3585" s="0" t="inlineStr">
+        <is>
+          <t>Saya mempunyai masalah tidur.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3586">
+      <c r="A3586" s="0">
+        <v>3716</v>
+      </c>
+      <c r="B3586" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3586" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3586" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3586" s="0" t="inlineStr">
+        <is>
+          <t>Saya berasa takut jika saya terpaksa tidur bersendirian.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3587">
+      <c r="A3587" s="0">
+        <v>3717</v>
+      </c>
+      <c r="B3587" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3587" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3587" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3587" s="0" t="inlineStr">
+        <is>
+          <t>Saya mempunyai masalah dengan selera makan saya.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3588">
+      <c r="A3588" s="0">
+        <v>3718</v>
+      </c>
+      <c r="B3588" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3588" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3588" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3588" s="0" t="inlineStr">
+        <is>
+          <t>Saya rasa pening atau hendak pengsan secara tibatiba tanpa sebab.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3589">
+      <c r="A3589" s="0">
+        <v>3719</v>
+      </c>
+      <c r="B3589" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3589" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3589" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3589" s="0" t="inlineStr">
+        <is>
+          <t>Saya perlu melakukan sesuatu perkara secara berulang-ulang (seperti basuh tangan, mengemas atau menyusun barang-barang di tempat tertentu).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3590">
+      <c r="A3590" s="0">
+        <v>3720</v>
+      </c>
+      <c r="B3590" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3590" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3590" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3590" s="0" t="inlineStr">
+        <is>
+          <t>Saya tidak mempunyai tenaga untuk melakukan sesuatu.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3591">
+      <c r="A3591" s="0">
+        <v>3721</v>
+      </c>
+      <c r="B3591" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3591" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3591" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3591" s="0" t="inlineStr">
+        <is>
+          <t>Saya tiba-tiba menjadi gementar atau menggigil tanpa apa-apa sebab.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3592">
+      <c r="A3592" s="0">
+        <v>3722</v>
+      </c>
+      <c r="B3592" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3592" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3592" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3592" s="0" t="inlineStr">
+        <is>
+          <t>Saya tidak boleh berfikir dengan jelas.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3593">
+      <c r="A3593" s="0">
+        <v>3723</v>
+      </c>
+      <c r="B3593" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3593" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3593" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3593" s="0" t="inlineStr">
+        <is>
+          <t>Saya berasa tidak bernilai.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3594">
+      <c r="A3594" s="0">
+        <v>3724</v>
+      </c>
+      <c r="B3594" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3594" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3594" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3594" s="0" t="inlineStr">
+        <is>
+          <t>Saya terpaksa memikirkan sesuatu perkara yang lain (seperti nombor atau perkataan) untuk menghentikan sesuatu perkara buruk daripada berlaku.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3595">
+      <c r="A3595" s="0">
+        <v>3725</v>
+      </c>
+      <c r="B3595" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3595" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3595" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3595" s="0" t="inlineStr">
+        <is>
+          <t>Saya memikirkan tentang kematian.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3596">
+      <c r="A3596" s="0">
+        <v>3726</v>
+      </c>
+      <c r="B3596" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3596" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3596" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3596" s="0" t="inlineStr">
+        <is>
+          <t>Saya rasa seperti saya tidak mahu bergerak.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3597">
+      <c r="A3597" s="0">
+        <v>3727</v>
+      </c>
+      <c r="B3597" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3597" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3597" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3597" s="0" t="inlineStr">
+        <is>
+          <t>Saya bimbang jika saya tiba-tiba akan berasa takut sedangkan tiada perkara untuk ditakuti.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3598">
+      <c r="A3598" s="0">
+        <v>3728</v>
+      </c>
+      <c r="B3598" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3598" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3598" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3598" s="0" t="inlineStr">
+        <is>
+          <t>Saya letih sangat.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3599">
+      <c r="A3599" s="0">
+        <v>3729</v>
+      </c>
+      <c r="B3599" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3599" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3599" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3599" s="0" t="inlineStr">
+        <is>
+          <t>Saya takut jika saya akan memperbodohkan diri saya di hadapan orang.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3600">
+      <c r="A3600" s="0">
+        <v>3730</v>
+      </c>
+      <c r="B3600" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3600" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3600" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3600" s="0" t="inlineStr">
+        <is>
+          <t>Saya perlu melakukan perkara dengan betul untuk menghentikan perkara buruk daripada berlaku.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3601">
+      <c r="A3601" s="0">
+        <v>3731</v>
+      </c>
+      <c r="B3601" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3601" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3601" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3601" s="0" t="inlineStr">
+        <is>
+          <t>Saya berasa gelisah.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3602">
+      <c r="A3602" s="0">
+        <v>3732</v>
+      </c>
+      <c r="B3602" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3602" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3602" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3602" s="0" t="inlineStr">
+        <is>
+          <t>Saya bimbang jika sesuatu yang buruk akan berlaku kepada saya.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3603">
+      <c r="A3603" s="0">
+        <v>3877</v>
+      </c>
+      <c r="B3603" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3603" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3603" s="0">
+        <v>88</v>
+      </c>
+      <c r="E3603" s="0" t="inlineStr">
+        <is>
+          <t>Little pleasure or little interest in doing things</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3604">
+      <c r="A3604" s="0">
+        <v>3878</v>
+      </c>
+      <c r="B3604" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3604" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3604" s="0">
+        <v>86</v>
+      </c>
+      <c r="E3604" s="0" t="inlineStr">
+        <is>
+          <t>Having little energy or feeling tired</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3605">
+      <c r="A3605" s="0">
+        <v>3879</v>
+      </c>
+      <c r="B3605" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3605" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3605" s="0">
+        <v>87</v>
+      </c>
+      <c r="E3605" s="0" t="inlineStr">
+        <is>
+          <t>Feeling negative about yourself or that you are a failure or have let your self or your family down</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3606">
+      <c r="A3606" s="0">
+        <v>3880</v>
+      </c>
+      <c r="B3606" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3606" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3606" s="0">
+        <v>89</v>
+      </c>
+      <c r="E3606" s="0" t="inlineStr">
+        <is>
+          <t>Moving or talking so slowly that other people could have noticed?  Or the opposite — being so fidgety or restless that you have been moving around a lot more than usual</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3607">
+      <c r="A3607" s="0">
+        <v>3881</v>
+      </c>
+      <c r="B3607" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3607" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3607" s="0">
+        <v>85</v>
+      </c>
+      <c r="E3607" s="0" t="inlineStr">
+        <is>
+          <t>Difficultés à s’endormir ou à rester endormi(e), ou dormir trop</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3608">
+      <c r="A3608" s="0">
+        <v>3882</v>
+      </c>
+      <c r="B3608" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3608" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3608" s="0">
+        <v>86</v>
+      </c>
+      <c r="E3608" s="0" t="inlineStr">
+        <is>
+          <t>Se sentir fatigué(e) ou manquer d’énergie</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3609">
+      <c r="A3609" s="0">
+        <v>3883</v>
+      </c>
+      <c r="B3609" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3609" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3609" s="0">
+        <v>91</v>
+      </c>
+      <c r="E3609" s="0" t="inlineStr">
+        <is>
+          <t>Avoir peu d’appétit ou manger trop</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3610">
+      <c r="A3610" s="0">
+        <v>3884</v>
+      </c>
+      <c r="B3610" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3610" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3610" s="0">
+        <v>87</v>
+      </c>
+      <c r="E3610" s="0" t="inlineStr">
+        <is>
+          <t>Avoir une mauvaise opinion de soi-même, ou avoir le sentiment d’être nul(le), ou d’avoir déçu sa famille ou s’être déçu(e)  soi-même</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3611">
+      <c r="A3611" s="0">
+        <v>3885</v>
+      </c>
+      <c r="B3611" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3611" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3611" s="0">
+        <v>92</v>
+      </c>
+      <c r="E3611" s="0" t="inlineStr">
+        <is>
+          <t>Avoir du mal à se concentrer, par exemple, pour lire le journal ou regarder la télévision</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3612">
+      <c r="A3612" s="0">
+        <v>3886</v>
+      </c>
+      <c r="B3612" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3612" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3612" s="0">
+        <v>89</v>
+      </c>
+      <c r="E3612" s="0" t="inlineStr">
+        <is>
+          <t>Bouger ou parler si lentement que les autres auraient pu le remarquer. Ou au contraire, être si agité(e) que vous avez eu du mal à tenir en place par rapport à d’habitude</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3613">
+      <c r="A3613" s="0">
+        <v>3887</v>
+      </c>
+      <c r="B3613" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3613" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3613" s="0">
+        <v>90</v>
+      </c>
+      <c r="E3613" s="0" t="inlineStr">
+        <is>
+          <t>Penser qu’il vaudrait mieux mourir ou envisager de vous faire du mal d’une manière ou d’une autre</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3614">
+      <c r="A3614" s="0">
+        <v>3780</v>
+      </c>
+      <c r="B3614" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3614" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3614" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3614" s="0" t="inlineStr">
+        <is>
+          <t>Unë shqetësohem për gjëra të ndryshme.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3615">
+      <c r="A3615" s="0">
+        <v>3781</v>
+      </c>
+      <c r="B3615" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3615" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3615" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3615" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e trishtuar ose bosh.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3616">
+      <c r="A3616" s="0">
+        <v>3782</v>
+      </c>
+      <c r="B3616" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3616" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3616" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3616" s="0" t="inlineStr">
+        <is>
+          <t>Kur kam një problem, më krijohet një ndjesi e çuditshme në stomak.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3617">
+      <c r="A3617" s="0">
+        <v>3783</v>
+      </c>
+      <c r="B3617" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3617" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3617" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3617" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem kur mendoj se nuk kam dalë mirë në një detyrë të caktuar.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3618">
+      <c r="A3618" s="0">
+        <v>3784</v>
+      </c>
+      <c r="B3618" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3618" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3618" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3618" s="0" t="inlineStr">
+        <is>
+          <t>Do ndihesha i/e frikësuar nga të qënurit vetëm në shtëpi.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3619">
+      <c r="A3619" s="0">
+        <v>3785</v>
+      </c>
+      <c r="B3619" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3619" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3619" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3619" s="0" t="inlineStr">
+        <is>
+          <t>Asgjë nuk është më aq argëtuese.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3620">
+      <c r="A3620" s="0">
+        <v>3786</v>
+      </c>
+      <c r="B3620" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3620" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3620" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3620" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e frikësuar kur kam për të bërë testim/provim.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3621">
+      <c r="A3621" s="0">
+        <v>3787</v>
+      </c>
+      <c r="B3621" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3621" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3621" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3621" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e shqetësuar kur mendoj që dikush është i nevrikosur me mua.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3622">
+      <c r="A3622" s="0">
+        <v>3788</v>
+      </c>
+      <c r="B3622" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3622" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3622" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3622" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem nga të qenurit larg prindërve të mi.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3623">
+      <c r="A3623" s="0">
+        <v>3789</v>
+      </c>
+      <c r="B3623" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3623" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3623" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3623" s="0" t="inlineStr">
+        <is>
+          <t>Më bezdisin mendimet ose imazhet e këqia ose qesharake në mendjen time.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3624">
+      <c r="A3624" s="0">
+        <v>3790</v>
+      </c>
+      <c r="B3624" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3624" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3624" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3624" s="0" t="inlineStr">
+        <is>
+          <t>Kam vështirësi për të fjetur.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3625">
+      <c r="A3625" s="0">
+        <v>3791</v>
+      </c>
+      <c r="B3625" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3625" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3625" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3625" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se do të kem rezultate jo të mira në detyrat e shkollës.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3626">
+      <c r="A3626" s="0">
+        <v>3792</v>
+      </c>
+      <c r="B3626" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3626" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3626" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3626" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se diçka e tmerrshme do t'i ndodhë dikujt në familjen time.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3627">
+      <c r="A3627" s="0">
+        <v>3793</v>
+      </c>
+      <c r="B3627" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3627" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3627" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3627" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem papritur sikur nuk mbushem dot me frymë pa pasur arsye specifike.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3628">
+      <c r="A3628" s="0">
+        <v>3794</v>
+      </c>
+      <c r="B3628" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3628" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3628" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3628" s="0" t="inlineStr">
+        <is>
+          <t>Kam probleme me oreksin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3629">
+      <c r="A3629" s="0">
+        <v>3795</v>
+      </c>
+      <c r="B3629" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3629" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3629" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3629" s="0" t="inlineStr">
+        <is>
+          <t>Kam nevojë të kontrolloj disa herë që i kam bërë gjërat siç duhet (si për shembull: çelësi është i fikur, dera është e mbyllur).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3630">
+      <c r="A3630" s="0">
+        <v>3796</v>
+      </c>
+      <c r="B3630" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3630" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3630" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3630" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e frikësuar nëse duhet të fle vetëm.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3631">
+      <c r="A3631" s="0">
+        <v>3797</v>
+      </c>
+      <c r="B3631" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3631" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3631" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3631" s="0" t="inlineStr">
+        <is>
+          <t>Kam vështirësi për të shkuar në shkollë në mëngjes, sepse ndihem nervoz/e ose i/e frikësuar.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3632">
+      <c r="A3632" s="0">
+        <v>3798</v>
+      </c>
+      <c r="B3632" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3632" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3632" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3632" s="0" t="inlineStr">
+        <is>
+          <t>Nuk kam energji për të bërë gjëra.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3633">
+      <c r="A3633" s="0">
+        <v>3799</v>
+      </c>
+      <c r="B3633" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3633" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3633" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3633" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se mos dukem qesharak/e.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3634">
+      <c r="A3634" s="0">
+        <v>3800</v>
+      </c>
+      <c r="B3634" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3634" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3634" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3634" s="0" t="inlineStr">
+        <is>
+          <t>Jam i/e lodhur shume.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3635">
+      <c r="A3635" s="0">
+        <v>3801</v>
+      </c>
+      <c r="B3635" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3635" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3635" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3635" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se do të më ndodhin gjëra të këqija.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3636">
+      <c r="A3636" s="0">
+        <v>3802</v>
+      </c>
+      <c r="B3636" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3636" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3636" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3636" s="0" t="inlineStr">
+        <is>
+          <t>Nuk mundem të largoj mendimet e këqija ose qesharake nga mendja ime.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3637">
+      <c r="A3637" s="0">
+        <v>3803</v>
+      </c>
+      <c r="B3637" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3637" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3637" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3637" s="0" t="inlineStr">
+        <is>
+          <t>Kur kam një problem, zemra ime rreh shumë shpejt.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3638">
+      <c r="A3638" s="0">
+        <v>3804</v>
+      </c>
+      <c r="B3638" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3638" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3638" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3638" s="0" t="inlineStr">
+        <is>
+          <t>Nuk mund të mendoj qartë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3639">
+      <c r="A3639" s="0">
+        <v>3805</v>
+      </c>
+      <c r="B3639" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3639" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3639" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3639" s="0" t="inlineStr">
+        <is>
+          <t>Papritur filloj të tundem ose dridhem, kur nuk ka asnjë arsye për këtë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3640">
+      <c r="A3640" s="0">
+        <v>3806</v>
+      </c>
+      <c r="B3640" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3640" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3640" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3640" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se diçka e keqe do të më ndodhë mua.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3641">
+      <c r="A3641" s="0">
+        <v>3807</v>
+      </c>
+      <c r="B3641" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3641" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3641" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3641" s="0" t="inlineStr">
+        <is>
+          <t>Kur kam një problem, ndjej që po dridhem.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3642">
+      <c r="A3642" s="0">
+        <v>3808</v>
+      </c>
+      <c r="B3642" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3642" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3642" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3642" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e pavlerë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3643">
+      <c r="A3643" s="0">
+        <v>3809</v>
+      </c>
+      <c r="B3643" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3643" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3643" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3643" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se mos bëj gabime.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3644">
+      <c r="A3644" s="0">
+        <v>3810</v>
+      </c>
+      <c r="B3644" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3644" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3644" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3644" s="0" t="inlineStr">
+        <is>
+          <t>Duhet të mendoj gjëra speciale (si numra ose fjalë të caktuara) që të ndaloj gjëra të këqija të ndodhin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3645">
+      <c r="A3645" s="0">
+        <v>3811</v>
+      </c>
+      <c r="B3645" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3645" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3645" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3645" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem çfarë mendojnë njerëzit e tjerë për mua.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3646">
+      <c r="A3646" s="0">
+        <v>3812</v>
+      </c>
+      <c r="B3646" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3646" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3646" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3646" s="0" t="inlineStr">
+        <is>
+          <t>Kam frikë të gjendem në vende me turma (si qendrat tregtare, kinema, autobusë ose parqe lojrash).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3647">
+      <c r="A3647" s="0">
+        <v>3813</v>
+      </c>
+      <c r="B3647" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3647" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3647" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3647" s="0" t="inlineStr">
+        <is>
+          <t>Papritur filloj të ndihem shumë i/e frikësuar pa asnjë arsye.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3648">
+      <c r="A3648" s="0">
+        <v>3814</v>
+      </c>
+      <c r="B3648" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3648" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3648" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3648" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se çfarë do të ndodhë në të ardhmen.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3649">
+      <c r="A3649" s="0">
+        <v>3815</v>
+      </c>
+      <c r="B3649" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3649" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3649" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3649" s="0" t="inlineStr">
+        <is>
+          <t>Papritur ndiej marramendje ose më bie të fikët kur nuk ka asnjë arsye për këtë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3650">
+      <c r="A3650" s="0">
+        <v>3816</v>
+      </c>
+      <c r="B3650" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3650" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3650" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3650" s="0" t="inlineStr">
+        <is>
+          <t>Mendoj rreth vdekjes.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3651">
+      <c r="A3651" s="0">
+        <v>3817</v>
+      </c>
+      <c r="B3651" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3651" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3651" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3651" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e frikësuar nëse kam për të folur përpara klasës.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3652">
+      <c r="A3652" s="0">
+        <v>3818</v>
+      </c>
+      <c r="B3652" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3652" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3652" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3652" s="0" t="inlineStr">
+        <is>
+          <t>Zemra ime fillon papritur të rrahë shumë shpejt pa arsye.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3653">
+      <c r="A3653" s="0">
+        <v>3819</v>
+      </c>
+      <c r="B3653" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3653" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3653" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3653" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem sikur nuk dua të lëviz.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3654">
+      <c r="A3654" s="0">
+        <v>3874</v>
+      </c>
+      <c r="B3654" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3654" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3654" s="0">
+        <v>89</v>
+      </c>
+      <c r="E3654" s="0" t="inlineStr">
+        <is>
+          <t>Moving or speaking so slowly that other people could have noticed?  Or the opposite — being so fidgety or restless that you have been moving around a lot more than usual</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3655">
+      <c r="A3655" s="0">
+        <v>3820</v>
+      </c>
+      <c r="B3655" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3655" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3655" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3655" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem se papritur do të përjetoj një ndjesi frike edhe pse nuk ka asgjë për të pasur frikë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3656">
+      <c r="A3656" s="0">
+        <v>3821</v>
+      </c>
+      <c r="B3656" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3656" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3656" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3656" s="0" t="inlineStr">
+        <is>
+          <t>Më duhet të bëj disa gjëra vazhdimisht duke i përsëritur (si larja e duarve, pastrimi ose vendosja e gjërave në një rend të caktuar).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3657">
+      <c r="A3657" s="0">
+        <v>3822</v>
+      </c>
+      <c r="B3657" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3657" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3657" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3657" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e frikësuar se do të dukem si budalla/e para njerëzve.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3658">
+      <c r="A3658" s="0">
+        <v>3823</v>
+      </c>
+      <c r="B3658" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3658" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3658" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3658" s="0" t="inlineStr">
+        <is>
+          <t>Më duhet të bëj disa gjëra në mënyrën e duhur që të parandaloj gjërat e këqija që të ndodhin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3659">
+      <c r="A3659" s="0">
+        <v>3824</v>
+      </c>
+      <c r="B3659" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3659" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3659" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3659" s="0" t="inlineStr">
+        <is>
+          <t>Shqetësohem kur shtrihem për të fjetur natën.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3660">
+      <c r="A3660" s="0">
+        <v>3825</v>
+      </c>
+      <c r="B3660" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3660" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3660" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3660" s="0" t="inlineStr">
+        <is>
+          <t>Do ndihesha i/e frikësuar nëse do të më duhej të qëndroja larg shtëpisë për një natë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3661">
+      <c r="A3661" s="0">
+        <v>3826</v>
+      </c>
+      <c r="B3661" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3661" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3661" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3661" s="0" t="inlineStr">
+        <is>
+          <t>Ndihem i/e shqetësuar vazhdimisht.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3662">
+      <c r="A3662" s="0">
+        <v>3827</v>
+      </c>
+      <c r="B3662" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3662" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3662" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3662" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet për gjëra të ndryshme.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3663">
+      <c r="A3663" s="0">
+        <v>3828</v>
+      </c>
+      <c r="B3663" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3663" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3663" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3663" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e trishtuar ose bosh.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3664">
+      <c r="A3664" s="0">
+        <v>3829</v>
+      </c>
+      <c r="B3664" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3664" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3664" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3664" s="0" t="inlineStr">
+        <is>
+          <t>Kur fëmija im ka probleme, i krijohet një ndjesi e çuditshme në stomak.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3665">
+      <c r="A3665" s="0">
+        <v>3830</v>
+      </c>
+      <c r="B3665" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3665" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3665" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3665" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet kur ai/ajo mendon se  ka bërë diçka jo në mënyrën e duhur.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3666">
+      <c r="A3666" s="0">
+        <v>3831</v>
+      </c>
+      <c r="B3666" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3666" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3666" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3666" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e frikësuar nga të ndenjurit vetëm në shtëpi.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3667">
+      <c r="A3667" s="0">
+        <v>3832</v>
+      </c>
+      <c r="B3667" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3667" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3667" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3667" s="0" t="inlineStr">
+        <is>
+          <t>Asgjë s'e argëton më aq shumë fëmijën tim.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3668">
+      <c r="A3668" s="0">
+        <v>3833</v>
+      </c>
+      <c r="B3668" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3668" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3668" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3668" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e frikësuar kur ka nje provim.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3669">
+      <c r="A3669" s="0">
+        <v>3834</v>
+      </c>
+      <c r="B3669" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3669" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3669" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3669" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet kur mendon se dikush është zemëruar me të.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3670">
+      <c r="A3670" s="0">
+        <v>3835</v>
+      </c>
+      <c r="B3670" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3670" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3670" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3670" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet nga të qenurit larg meje.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3671">
+      <c r="A3671" s="0">
+        <v>3836</v>
+      </c>
+      <c r="B3671" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3671" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3671" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3671" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet nga mendime ose figura të këqia ose qesharake në mendjen e tij/saj.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3672">
+      <c r="A3672" s="0">
+        <v>3837</v>
+      </c>
+      <c r="B3672" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3672" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3672" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3672" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka probleme me gjumin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3673">
+      <c r="A3673" s="0">
+        <v>3838</v>
+      </c>
+      <c r="B3673" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3673" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3673" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3673" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se do të dalë keq me detyrat në shkollën.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3674">
+      <c r="A3674" s="0">
+        <v>3839</v>
+      </c>
+      <c r="B3674" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3674" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3674" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3674" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se diçka e tmerrshme do i ndodhë dikujt në familje.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3675">
+      <c r="A3675" s="0">
+        <v>3840</v>
+      </c>
+      <c r="B3675" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3675" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3675" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3675" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im papritur ndihet sikur nuk mund të marrë frymë edhe pse nuk ka asnjë arsye për këtë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3676">
+      <c r="A3676" s="0">
+        <v>3841</v>
+      </c>
+      <c r="B3676" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3676" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3676" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3676" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka probleme me oreksin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3677">
+      <c r="A3677" s="0">
+        <v>3842</v>
+      </c>
+      <c r="B3677" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3677" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3677" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3677" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka nevojë të kontrollojë vazhdimisht në mënyrë të përsëritur nëse i ka bërë gjërat në mënyrën e duhur (për shembull: çelësi është i fikur, dera është e kyçur).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3678">
+      <c r="A3678" s="0">
+        <v>3843</v>
+      </c>
+      <c r="B3678" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3678" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3678" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3678" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka frikë të flejë vetëm.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3679">
+      <c r="A3679" s="0">
+        <v>3844</v>
+      </c>
+      <c r="B3679" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3679" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3679" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3679" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka probleme për të shkuar në shkollë në mëngjes sepse është nervoz/e ose ka frikë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3680">
+      <c r="A3680" s="0">
+        <v>3845</v>
+      </c>
+      <c r="B3680" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3680" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3680" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3680" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im nuk ka energji për të bërë gjëra.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3681">
+      <c r="A3681" s="0">
+        <v>3846</v>
+      </c>
+      <c r="B3681" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3681" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3681" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3681" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se mos duket si budalla/qe.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3682">
+      <c r="A3682" s="0">
+        <v>3847</v>
+      </c>
+      <c r="B3682" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3682" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3682" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3682" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im është i/e lodhur gjithë kohës.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3683">
+      <c r="A3683" s="0">
+        <v>3848</v>
+      </c>
+      <c r="B3683" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3683" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3683" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3683" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se mund t'i ndodhin gjëra të këqija.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3684">
+      <c r="A3684" s="0">
+        <v>3849</v>
+      </c>
+      <c r="B3684" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3684" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3684" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3684" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im nuk po arrin të largojë mendimet e këqija ose qesharake nga koka.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3685">
+      <c r="A3685" s="0">
+        <v>3850</v>
+      </c>
+      <c r="B3685" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3685" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3685" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3685" s="0" t="inlineStr">
+        <is>
+          <t>Kur fëmija im ka një problem, zemra fillon t'i rrahë shumë shpejt.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3686">
+      <c r="A3686" s="0">
+        <v>3851</v>
+      </c>
+      <c r="B3686" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3686" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3686" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3686" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im nuk mendon dot qartësisht.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3687">
+      <c r="A3687" s="0">
+        <v>3852</v>
+      </c>
+      <c r="B3687" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3687" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3687" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3687" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im papritur fillon të tundet ose të dridhet edhe pse nuk ka asnjë arsye për këtë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3688">
+      <c r="A3688" s="0">
+        <v>3853</v>
+      </c>
+      <c r="B3688" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3688" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3688" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3688" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se diçka e keqe do t'i ndodhë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3689">
+      <c r="A3689" s="0">
+        <v>3854</v>
+      </c>
+      <c r="B3689" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3689" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3689" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3689" s="0" t="inlineStr">
+        <is>
+          <t>Kur fëmija im ka ndonjë problem, ai/ajo fillon të dridhet.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3690">
+      <c r="A3690" s="0">
+        <v>3855</v>
+      </c>
+      <c r="B3690" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3690" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3690" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3690" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e pavlerë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3691">
+      <c r="A3691" s="0">
+        <v>3856</v>
+      </c>
+      <c r="B3691" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3691" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3691" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3691" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se mos bën gabime.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3692">
+      <c r="A3692" s="0">
+        <v>3857</v>
+      </c>
+      <c r="B3692" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3692" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3692" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3692" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im duhet të mendojë gjëra speciale (si numra ose fjalë specifike) që të ndalojë gjërat e këqija të ndodhin.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3693">
+      <c r="A3693" s="0">
+        <v>3858</v>
+      </c>
+      <c r="B3693" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3693" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3693" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3693" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se çfarë të tjerët mendojnë për të.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3694">
+      <c r="A3694" s="0">
+        <v>3859</v>
+      </c>
+      <c r="B3694" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3694" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3694" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3694" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka frikë të jetë në vende të mbushura me njerëz (si qendra tregtare, kinema, autobusë, kënde lojërash të mbushura me njerëz).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3695">
+      <c r="A3695" s="0">
+        <v>3860</v>
+      </c>
+      <c r="B3695" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3695" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3695" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3695" s="0" t="inlineStr">
+        <is>
+          <t>Krejt papritur fëmija im do ndihet i/e frikësuar pa pasur arsye.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3696">
+      <c r="A3696" s="0">
+        <v>3861</v>
+      </c>
+      <c r="B3696" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3696" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3696" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3696" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se çfarë do të ndodhë në të ardhmen.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3697">
+      <c r="A3697" s="0">
+        <v>3862</v>
+      </c>
+      <c r="B3697" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3697" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3697" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3697" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im krejt papritur ka marramendje ose i bie të fikët pa pasur arsye.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3698">
+      <c r="A3698" s="0">
+        <v>3863</v>
+      </c>
+      <c r="B3698" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3698" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3698" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3698" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im mendon për vdekjen.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3699">
+      <c r="A3699" s="0">
+        <v>3864</v>
+      </c>
+      <c r="B3699" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3699" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3699" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3699" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e frikësuar nëse i duhet të flasë para klase.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3700">
+      <c r="A3700" s="0">
+        <v>3865</v>
+      </c>
+      <c r="B3700" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3700" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3700" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3700" s="0" t="inlineStr">
+        <is>
+          <t>Zemra e fëmijës sim fillon rrahë krejt papritur pa arsye.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3701">
+      <c r="A3701" s="0">
+        <v>3866</v>
+      </c>
+      <c r="B3701" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3701" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3701" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3701" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet sikur nuk dëshiron të lëvizë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3702">
+      <c r="A3702" s="0">
+        <v>3867</v>
+      </c>
+      <c r="B3702" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3702" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3702" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3702" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet se papritur do të përjetojë një ndjesi frike edhe pse nuk ka asgjë për të pasur frikë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3703">
+      <c r="A3703" s="0">
+        <v>3868</v>
+      </c>
+      <c r="B3703" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3703" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3703" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3703" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka nevojë të bëjë disa gjëra vazhdimisht duke i përsëritur (si larja e duarve, pastrimi ose vendosja e gjërave në një rend të caktuar).</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3704">
+      <c r="A3704" s="0">
+        <v>3869</v>
+      </c>
+      <c r="B3704" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3704" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3704" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3704" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im frikësohet se mos do ngjajë si budalla/e përpara njerëzve.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3705">
+      <c r="A3705" s="0">
+        <v>3870</v>
+      </c>
+      <c r="B3705" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3705" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3705" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3705" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ka nevojë të bëjë disa gjëra në mënyrën e duhur që të parandalojë gjërat e këqija.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3706">
+      <c r="A3706" s="0">
+        <v>3871</v>
+      </c>
+      <c r="B3706" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3706" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3706" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3706" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im shqetësohet kur shtrihet për të fjetur në mbrëmje.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3707">
+      <c r="A3707" s="0">
+        <v>3872</v>
+      </c>
+      <c r="B3707" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3707" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3707" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3707" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im do të ndihej i/e frikësuar nëse do t'i duhet të qëndronte larg shtëpisë për një natë.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3708">
+      <c r="A3708" s="0">
+        <v>3873</v>
+      </c>
+      <c r="B3708" s="0">
+        <v>42</v>
+      </c>
+      <c r="C3708" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3708" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3708" s="0" t="inlineStr">
+        <is>
+          <t>Fëmija im ndihet i/e shqetësuar vazhdimisht.</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3709">
+      <c r="A3709" s="0">
+        <v>3875</v>
+      </c>
+      <c r="B3709" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3709" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3709" s="0">
+        <v>88</v>
+      </c>
+      <c r="E3709" s="0" t="inlineStr">
+        <is>
+          <t>Peu d’intérêt ou de plaisir à faire les choses</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3710">
+      <c r="A3710" s="0">
+        <v>3876</v>
+      </c>
+      <c r="B3710" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3710" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3710" s="0">
+        <v>84</v>
+      </c>
+      <c r="E3710" s="0" t="inlineStr">
+        <is>
+          <t>Être triste, déprimé(e) ou désespéré(e)</t>
         </is>
       </c>
     </row>
